--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmayores_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmayores_a_2019_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:01</t>
+    <t xml:space="preserve">2026-09-24 00:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -559,7 +559,7 @@
         <v>-0.36</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -578,7 +578,7 @@
         <v>-0.51</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G3" s="2"/>
     </row>
@@ -597,7 +597,7 @@
         <v>-0.26</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -616,7 +616,7 @@
         <v>0.29</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -635,7 +635,7 @@
         <v>0.42</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -650,16 +650,16 @@
         <v>0.24</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="8">
@@ -670,19 +670,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="9">
@@ -693,19 +693,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.02</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="11">
@@ -739,19 +739,19 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="12">
@@ -762,19 +762,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13">
@@ -788,16 +788,16 @@
         <v>0.53</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0.25</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="14">
@@ -817,7 +817,7 @@
         <v>0.09</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>-0.38</v>
@@ -840,7 +840,7 @@
         <v>-0.13</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-0.23</v>
@@ -854,19 +854,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17">
@@ -877,19 +877,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>-0.18</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="18">
@@ -907,7 +907,7 @@
         <v>-0.66</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2"/>
     </row>
@@ -919,19 +919,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="20">
@@ -942,16 +942,16 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.12</v>
@@ -965,19 +965,19 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
